--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MISSOURI_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/MISSOURI_2015.xlsx
@@ -3138,7 +3138,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C155">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C252">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="B586" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C586">
